--- a/api/static/pert.xlsx
+++ b/api/static/pert.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anama\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anama\OneDrive\Documents\Faculdade\Iniciação Científica\ARNA_UFPE\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7778AE27-CF8C-4F50-9EB9-E466C0B3FD5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1777D654-1A34-435B-A27B-2D5102A53218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7EB555F7-2C2B-4388-8B33-737FD34076B1}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
   <si>
     <t>Precedentes</t>
   </si>
@@ -77,10 +77,13 @@
     <t>t_provavel</t>
   </si>
   <si>
-    <t>D,E</t>
-  </si>
-  <si>
-    <t>G,H</t>
+    <t>inicio</t>
+  </si>
+  <si>
+    <t>D, E</t>
+  </si>
+  <si>
+    <t>G, H</t>
   </si>
 </sst>
 </file>
@@ -517,16 +520,16 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="G2" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -539,19 +542,19 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="G3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H3" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
@@ -564,19 +567,19 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="G4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H4" t="s">
         <v>3</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
@@ -589,19 +592,19 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="G5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
         <v>4</v>
       </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
       <c r="K5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
@@ -614,19 +617,19 @@
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="G6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H6" t="s">
         <v>4</v>
       </c>
       <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
         <v>8</v>
-      </c>
-      <c r="J6">
-        <v>12</v>
-      </c>
-      <c r="K6">
-        <v>10</v>
       </c>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
@@ -639,19 +642,19 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="G7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" t="s">
+        <v>4</v>
+      </c>
+      <c r="I7">
         <v>8</v>
       </c>
-      <c r="H7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
       <c r="J7">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
@@ -664,19 +667,19 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="G8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H8" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I8">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J8">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
@@ -689,19 +692,19 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="G9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9">
+        <v>7</v>
+      </c>
+      <c r="J9">
+        <v>11</v>
+      </c>
+      <c r="K9">
         <v>8</v>
-      </c>
-      <c r="I9">
-        <v>3</v>
-      </c>
-      <c r="J9">
-        <v>6</v>
-      </c>
-      <c r="K9">
-        <v>5</v>
       </c>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
@@ -714,10 +717,19 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="G10" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H10" t="s">
-        <v>15</v>
+        <v>8</v>
+      </c>
+      <c r="I10">
+        <v>3</v>
+      </c>
+      <c r="J10">
+        <v>6</v>
+      </c>
+      <c r="K10">
+        <v>5</v>
       </c>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
@@ -735,11 +747,12 @@
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
+      <c r="G11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H11" t="s">
+        <v>16</v>
+      </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>

--- a/api/static/pert.xlsx
+++ b/api/static/pert.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anama\OneDrive\Documents\Faculdade\Iniciação Científica\ARNA_UFPE\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1777D654-1A34-435B-A27B-2D5102A53218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64E999AF-38D9-4E33-B3A7-73E27985D025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7EB555F7-2C2B-4388-8B33-737FD34076B1}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>Precedentes</t>
   </si>
@@ -42,30 +42,6 @@
   </si>
   <si>
     <t>fim</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>H</t>
   </si>
   <si>
     <t>t_otimista</t>
@@ -80,10 +56,10 @@
     <t>inicio</t>
   </si>
   <si>
-    <t>D, E</t>
+    <t>4, 5</t>
   </si>
   <si>
-    <t>G, H</t>
+    <t>7, 8</t>
   </si>
 </sst>
 </file>
@@ -493,20 +469,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="G1" t="s">
+      <c r="A1" t="s">
         <v>1</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="I1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" t="s">
-        <v>13</v>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
       </c>
       <c r="L1" s="1"/>
       <c r="M1" s="2"/>
@@ -519,16 +495,16 @@
       <c r="U1" s="3"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="D2">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="E2">
         <v>0</v>
       </c>
       <c r="M2" s="2"/>
@@ -541,19 +517,19 @@
       <c r="U2" s="3"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="G3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3">
         <v>2</v>
       </c>
-      <c r="J3">
+      <c r="D3">
         <v>8</v>
       </c>
-      <c r="K3">
+      <c r="E3">
         <v>5</v>
       </c>
       <c r="M3" s="2"/>
@@ -566,19 +542,19 @@
       <c r="U3" s="3"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="G4" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
         <v>3</v>
       </c>
-      <c r="I4">
-        <v>3</v>
-      </c>
-      <c r="J4">
+      <c r="D4">
         <v>10</v>
       </c>
-      <c r="K4">
+      <c r="E4">
         <v>6</v>
       </c>
       <c r="M4" s="2"/>
@@ -591,19 +567,19 @@
       <c r="U4" s="3"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="G5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="A5">
         <v>3</v>
       </c>
-      <c r="I5">
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="J5">
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
         <v>4</v>
       </c>
-      <c r="K5">
+      <c r="E5">
         <v>5</v>
       </c>
       <c r="M5" s="2"/>
@@ -616,19 +592,19 @@
       <c r="U5" s="3"/>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="G6" t="s">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
         <v>6</v>
       </c>
-      <c r="H6" t="s">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
+      <c r="E6">
         <v>8</v>
       </c>
       <c r="M6" s="2"/>
@@ -641,19 +617,19 @@
       <c r="U6" s="3"/>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="G7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H7" t="s">
-        <v>4</v>
-      </c>
-      <c r="I7">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
         <v>8</v>
       </c>
-      <c r="J7">
+      <c r="D7">
         <v>12</v>
       </c>
-      <c r="K7">
+      <c r="E7">
         <v>10</v>
       </c>
       <c r="M7" s="2"/>
@@ -666,19 +642,19 @@
       <c r="U7" s="3"/>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="G8" t="s">
-        <v>8</v>
-      </c>
-      <c r="H8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I8">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
         <v>3</v>
       </c>
-      <c r="J8">
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8">
         <v>6</v>
       </c>
-      <c r="K8">
+      <c r="E8">
         <v>5</v>
       </c>
       <c r="M8" s="2"/>
@@ -691,19 +667,19 @@
       <c r="U8" s="3"/>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="G9" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9">
+      <c r="A9">
         <v>7</v>
       </c>
-      <c r="J9">
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7</v>
+      </c>
+      <c r="D9">
         <v>11</v>
       </c>
-      <c r="K9">
+      <c r="E9">
         <v>8</v>
       </c>
       <c r="M9" s="2"/>
@@ -716,19 +692,19 @@
       <c r="U9" s="3"/>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="G10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H10" t="s">
+      <c r="A10">
         <v>8</v>
       </c>
-      <c r="I10">
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10">
         <v>3</v>
       </c>
-      <c r="J10">
+      <c r="D10">
         <v>6</v>
       </c>
-      <c r="K10">
+      <c r="E10">
         <v>5</v>
       </c>
       <c r="M10" s="2"/>
@@ -741,18 +717,13 @@
       <c r="U10" s="3"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
+      <c r="A11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
       <c r="F11" s="2"/>
-      <c r="G11" t="s">
-        <v>2</v>
-      </c>
-      <c r="H11" t="s">
-        <v>16</v>
-      </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
